--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_wb_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_wb_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -828,7 +828,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>16-09-2021 08:30</t>
+          <t>2021-09-16 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>28-04-2021 08:30</t>
+          <t>2021-04-28 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="inlineStr"/>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -9195,7 +9195,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -10125,7 +10125,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="inlineStr"/>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10683,7 +10683,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -10869,7 +10869,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -11055,7 +11055,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -11241,7 +11241,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -11427,7 +11427,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="inlineStr"/>
@@ -11613,7 +11613,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="inlineStr"/>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="inlineStr"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr"/>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16442,7 +16442,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16822,7 +16822,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -17012,7 +17012,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -17107,7 +17107,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -17297,7 +17297,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -17962,7 +17962,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -18057,7 +18057,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -18152,7 +18152,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18645,7 +18645,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="inlineStr"/>
@@ -19130,7 +19130,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="inlineStr"/>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -19318,7 +19318,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="n">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="n">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="n">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>25-06-2021 08:30</t>
+          <t>2021-06-25 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>16-07-2021 08:30</t>
+          <t>2021-07-16 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>27-08-2021 08:30</t>
+          <t>2021-08-27 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="n">
@@ -19888,7 +19888,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>29-09-2021 08:30</t>
+          <t>2021-09-29 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="n">
@@ -20078,7 +20078,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="n">
@@ -20173,7 +20173,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -20359,7 +20359,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="inlineStr"/>
@@ -20452,7 +20452,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="n">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="n">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20747,7 +20747,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20840,7 +20840,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20933,7 +20933,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="n">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="n">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="n">
@@ -21218,7 +21218,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="n">
@@ -21313,7 +21313,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="n">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="n">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="n">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>25-08-2021 08:30</t>
+          <t>2021-08-25 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="n">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>27-09-2021 08:30</t>
+          <t>2021-09-27 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="n">
@@ -21788,7 +21788,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="n">
@@ -21883,7 +21883,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="n">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="n">
@@ -22168,7 +22168,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="n">
@@ -22263,7 +22263,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="n">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="n">
@@ -22453,7 +22453,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>29-06-2021 08:30</t>
+          <t>2021-06-29 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="n">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>23-07-2021 08:30</t>
+          <t>2021-07-23 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="n">
@@ -22643,7 +22643,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>23-08-2021 08:30</t>
+          <t>2021-08-23 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="n">
@@ -22738,7 +22738,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>24-09-2021 08:30</t>
+          <t>2021-09-24 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="n">
@@ -22833,7 +22833,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="n">
@@ -22928,7 +22928,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>12-11-2021 08:30</t>
+          <t>2021-12-11 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="n">
@@ -23023,7 +23023,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="n">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="n">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="n">
@@ -23308,7 +23308,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>29-04-2021 08:30</t>
+          <t>2021-04-29 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="n">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="n">
@@ -23498,7 +23498,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>27-08-2021 08:30</t>
+          <t>2021-08-27 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="n">
@@ -23593,7 +23593,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="n">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="n">
@@ -23783,7 +23783,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="n">
@@ -23878,7 +23878,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>17-12-2021 08:30</t>
+          <t>2021-12-17 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="n">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr"/>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr"/>
@@ -24159,7 +24159,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr"/>
@@ -24252,7 +24252,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="inlineStr"/>
@@ -24345,7 +24345,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="inlineStr"/>
@@ -24438,7 +24438,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="inlineStr"/>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="n">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="n">
@@ -24721,7 +24721,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="n">
@@ -24816,7 +24816,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="n">
@@ -24911,7 +24911,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -25101,7 +25101,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="n">
@@ -25196,7 +25196,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="n">
@@ -25291,7 +25291,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="n">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="n">
@@ -25481,7 +25481,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="n">
@@ -25576,7 +25576,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="inlineStr"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="inlineStr"/>
@@ -25762,7 +25762,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="inlineStr"/>
@@ -25855,7 +25855,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="n">
@@ -25956,7 +25956,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="n">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="n">
@@ -26152,7 +26152,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="n">
@@ -26247,7 +26247,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="n">
@@ -26342,7 +26342,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="n">
@@ -26437,7 +26437,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>25-06-2021 08:30</t>
+          <t>2021-06-25 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="n">
@@ -26532,7 +26532,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>16-07-2021 08:30</t>
+          <t>2021-07-16 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="n">
@@ -26627,7 +26627,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>27-08-2021 08:30</t>
+          <t>2021-08-27 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="n">
@@ -26722,7 +26722,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>29-09-2021 08:30</t>
+          <t>2021-09-29 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="n">
@@ -26817,7 +26817,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="n">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>29-12-2021 08:30</t>
+          <t>2021-12-29 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="n">
@@ -27007,7 +27007,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="n">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="n">
@@ -27209,7 +27209,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="inlineStr"/>
@@ -27395,7 +27395,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="inlineStr"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="inlineStr"/>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="inlineStr"/>
@@ -27674,7 +27674,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>30-03-2021 08:30</t>
+          <t>2021-03-30 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="inlineStr"/>
@@ -27767,7 +27767,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="n">
@@ -27868,7 +27868,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="n">
@@ -27969,7 +27969,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="n">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="n">
@@ -28171,7 +28171,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="n">
@@ -28272,7 +28272,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="n">
@@ -28373,7 +28373,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="n">
@@ -28474,7 +28474,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="n">
@@ -28573,7 +28573,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="n">
@@ -28668,7 +28668,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="n">
@@ -28763,7 +28763,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="n">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="n">
@@ -28953,7 +28953,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="n">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>29-07-2021 08:30</t>
+          <t>2021-07-29 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="n">
@@ -29143,7 +29143,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>25-08-2021 08:30</t>
+          <t>2021-08-25 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="n">
@@ -29238,7 +29238,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="n">
@@ -29333,7 +29333,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="n">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="n">
@@ -29523,7 +29523,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="n">
@@ -29618,7 +29618,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="n">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="n">
@@ -29808,7 +29808,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="inlineStr"/>
@@ -29901,7 +29901,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="n">
@@ -29996,7 +29996,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="n">
@@ -30091,7 +30091,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="n">
@@ -30186,7 +30186,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="n">
@@ -30281,7 +30281,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="n">
@@ -30376,7 +30376,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="n">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="n">
@@ -30566,7 +30566,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="n">
@@ -30661,7 +30661,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="n">
@@ -30756,7 +30756,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="n">
@@ -30857,7 +30857,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="n">
@@ -30958,7 +30958,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="inlineStr"/>
@@ -31051,7 +31051,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="inlineStr"/>
@@ -31144,7 +31144,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="inlineStr"/>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>24-01-2021 08:30</t>
+          <t>2021-01-24 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="inlineStr"/>
@@ -31330,7 +31330,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="inlineStr"/>
@@ -31423,7 +31423,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="inlineStr"/>
@@ -31516,7 +31516,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="inlineStr"/>
@@ -31609,7 +31609,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="inlineStr"/>
@@ -31702,7 +31702,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="inlineStr"/>
@@ -31795,7 +31795,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="n">
@@ -31896,7 +31896,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="n">
@@ -31997,7 +31997,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="n">
@@ -32096,7 +32096,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="n">
@@ -32197,7 +32197,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="inlineStr"/>
@@ -32290,7 +32290,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="inlineStr"/>
@@ -32383,7 +32383,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="inlineStr"/>
@@ -32476,7 +32476,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="inlineStr"/>
@@ -32569,7 +32569,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="inlineStr"/>
@@ -32662,7 +32662,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="inlineStr"/>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="inlineStr"/>
@@ -32848,7 +32848,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="inlineStr"/>
@@ -32941,7 +32941,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="inlineStr"/>
@@ -33034,7 +33034,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="inlineStr"/>
@@ -33127,7 +33127,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="inlineStr"/>
@@ -33220,7 +33220,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="inlineStr"/>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="inlineStr"/>
@@ -33406,7 +33406,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="inlineStr"/>
@@ -33499,7 +33499,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -33592,7 +33592,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="inlineStr"/>
@@ -33685,7 +33685,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="inlineStr"/>
@@ -33778,7 +33778,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="inlineStr"/>
@@ -33871,7 +33871,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="inlineStr"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="inlineStr"/>
@@ -34057,7 +34057,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -34150,7 +34150,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="inlineStr"/>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="inlineStr"/>
@@ -34336,7 +34336,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="inlineStr"/>
@@ -34429,7 +34429,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="inlineStr"/>
@@ -34522,7 +34522,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="inlineStr"/>
@@ -34615,7 +34615,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="inlineStr"/>
@@ -34708,7 +34708,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="inlineStr"/>
@@ -34801,7 +34801,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="inlineStr"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="inlineStr"/>
@@ -34987,7 +34987,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="inlineStr"/>
@@ -35080,7 +35080,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="inlineStr"/>
@@ -35173,7 +35173,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="inlineStr"/>
@@ -35266,7 +35266,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="inlineStr"/>
@@ -35359,7 +35359,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="inlineStr"/>
@@ -35452,7 +35452,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="inlineStr"/>
@@ -35545,7 +35545,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="inlineStr"/>
@@ -35638,7 +35638,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="inlineStr"/>
@@ -35731,7 +35731,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="inlineStr"/>
@@ -35824,7 +35824,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="inlineStr"/>
@@ -35917,7 +35917,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="inlineStr"/>
@@ -36010,7 +36010,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="inlineStr"/>
@@ -36103,7 +36103,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="inlineStr"/>
@@ -36196,7 +36196,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="inlineStr"/>
@@ -36289,7 +36289,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="inlineStr"/>
@@ -36382,7 +36382,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="inlineStr"/>
@@ -36475,7 +36475,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="inlineStr"/>
@@ -36568,7 +36568,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="inlineStr"/>
@@ -36661,7 +36661,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="inlineStr"/>
@@ -36754,7 +36754,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="inlineStr"/>
@@ -36847,7 +36847,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="inlineStr"/>
@@ -36940,7 +36940,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="inlineStr"/>
@@ -37033,7 +37033,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="inlineStr"/>
@@ -37126,7 +37126,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="inlineStr"/>
@@ -37219,7 +37219,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="inlineStr"/>
@@ -37312,7 +37312,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="inlineStr"/>
@@ -37405,7 +37405,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="inlineStr"/>
@@ -37498,7 +37498,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="n">
@@ -37593,7 +37593,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="n">
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="n">
@@ -37783,7 +37783,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="n">
@@ -37878,7 +37878,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="n">
@@ -37973,7 +37973,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="n">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="n">
@@ -38163,7 +38163,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>16-09-2021 08:30</t>
+          <t>2021-09-16 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="n">
@@ -38258,7 +38258,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="n">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="n">
@@ -38448,7 +38448,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="n">
@@ -38543,7 +38543,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="n">
@@ -38644,7 +38644,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="n">
@@ -38745,7 +38745,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="n">
@@ -38846,7 +38846,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="n">
@@ -38947,7 +38947,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="n">
@@ -39048,7 +39048,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="n">
@@ -39149,7 +39149,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="n">
@@ -39250,7 +39250,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="n">
@@ -39351,7 +39351,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="n">
@@ -39446,7 +39446,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="n">
@@ -39541,7 +39541,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="n">
@@ -39636,7 +39636,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="n">
@@ -39731,7 +39731,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>25-06-2021 08:30</t>
+          <t>2021-06-25 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="n">
@@ -39826,7 +39826,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>16-07-2021 08:30</t>
+          <t>2021-07-16 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="n">
@@ -39921,7 +39921,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>27-08-2021 08:30</t>
+          <t>2021-08-27 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="n">
@@ -40016,7 +40016,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>29-09-2021 08:30</t>
+          <t>2021-09-29 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="n">
@@ -40111,7 +40111,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="n">
@@ -40206,7 +40206,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="inlineStr"/>
@@ -40299,7 +40299,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="inlineStr"/>
@@ -40392,7 +40392,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="inlineStr"/>
@@ -40485,7 +40485,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="inlineStr"/>
@@ -40578,7 +40578,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="n">
@@ -40679,7 +40679,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="n">
@@ -40780,7 +40780,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="n">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="n">
@@ -40982,7 +40982,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="inlineStr"/>
@@ -41075,7 +41075,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="inlineStr"/>
@@ -41168,7 +41168,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="inlineStr"/>
@@ -41261,7 +41261,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="n">
@@ -41362,7 +41362,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="n">
@@ -41463,7 +41463,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="inlineStr"/>
@@ -41556,7 +41556,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="inlineStr"/>
@@ -41649,7 +41649,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="inlineStr"/>
@@ -41742,7 +41742,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="inlineStr"/>
@@ -41835,7 +41835,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="inlineStr"/>
@@ -41928,7 +41928,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>30-03-2021 08:30</t>
+          <t>2021-03-30 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="inlineStr"/>
@@ -42021,7 +42021,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="n">
@@ -42122,7 +42122,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="n">
@@ -42223,7 +42223,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="inlineStr"/>
@@ -42316,7 +42316,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="inlineStr"/>
@@ -42409,7 +42409,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="inlineStr"/>
@@ -42502,7 +42502,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="inlineStr"/>
@@ -42595,7 +42595,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="inlineStr"/>
@@ -42688,7 +42688,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="inlineStr"/>
@@ -42781,7 +42781,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="n">
@@ -42882,7 +42882,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="n">
@@ -42983,7 +42983,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="inlineStr"/>
@@ -43076,7 +43076,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="inlineStr"/>
@@ -43169,7 +43169,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="inlineStr"/>
@@ -43262,7 +43262,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="inlineStr"/>
@@ -43355,7 +43355,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="inlineStr"/>
@@ -43448,7 +43448,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="inlineStr"/>
@@ -43541,7 +43541,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="inlineStr"/>
@@ -43634,7 +43634,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="inlineStr"/>
@@ -43727,7 +43727,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="inlineStr"/>
@@ -43820,7 +43820,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="n">
@@ -43915,7 +43915,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="n">
@@ -44010,7 +44010,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="n">
@@ -44105,7 +44105,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>28-04-2021 08:30</t>
+          <t>2021-04-28 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="n">
@@ -44200,7 +44200,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>30-07-2021 08:30</t>
+          <t>2021-07-30 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="n">
@@ -44295,7 +44295,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>24-09-2021 08:30</t>
+          <t>2021-09-24 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="n">
@@ -44390,7 +44390,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="n">
@@ -44485,7 +44485,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>30-12-2021 08:30</t>
+          <t>2021-12-30 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="n">
@@ -44580,7 +44580,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="n">
@@ -44675,7 +44675,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="n">
@@ -44770,7 +44770,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="n">
@@ -44865,7 +44865,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="n">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>25-06-2021 08:30</t>
+          <t>2021-06-25 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="n">
@@ -45055,7 +45055,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>16-07-2021 08:30</t>
+          <t>2021-07-16 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="n">
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>27-08-2021 08:30</t>
+          <t>2021-08-27 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="n">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>29-09-2021 08:30</t>
+          <t>2021-09-29 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="n">
@@ -45340,7 +45340,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="n">
@@ -45435,7 +45435,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="n">
